--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Quest.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Quest.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="804">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="809">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1439,6 +1439,21 @@
   </si>
   <si>
     <t xml:space="preserve">into_darkness6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|죽은 자의 동굴에서 할 일은 끝났다. 거점에서 케틀과 이야기해 보자.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|Your business in the Crypt of the Damned is done. Time to return to your base and talk to Kettle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|死者の洞窟での用は終わった。拠点でケトルに話しかけよう。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">into_darkness7</t>
   </si>
   <si>
     <t xml:space="preserve">|죽은 자의 동굴에서 할 일은 끝났다. 거점에서 이스시즐이 접촉해 오길 기다리자.</t>
@@ -2932,7 +2947,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N146"/>
+  <dimension ref="A1:N147"/>
   <sheetFormatPr defaultColWidth="8.62109375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="1" style="0" width="16.15"/>
@@ -4794,49 +4809,49 @@
         <v>469</v>
       </c>
       <c r="B92" s="0" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="F92" s="0" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G92" s="0" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H92" s="0" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B93" s="0" t="s">
-        <v>474</v>
-      </c>
-      <c r="C93" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="F93" s="0" t="s">
         <v>475</v>
       </c>
-      <c r="D93" s="0" t="s">
+      <c r="G93" s="0" t="s">
         <v>476</v>
       </c>
-      <c r="E93" s="0" t="s">
+      <c r="H93" s="0" t="s">
         <v>477</v>
-      </c>
-      <c r="F93" s="0" t="s">
-        <v>478</v>
-      </c>
-      <c r="G93" s="0" t="s">
-        <v>479</v>
-      </c>
-      <c r="H93" s="0" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="C94" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="D94" s="0" t="s">
         <v>481</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="E94" s="0" t="s">
         <v>482</v>
       </c>
       <c r="F94" s="0" t="s">
@@ -4854,136 +4869,127 @@
         <v>486</v>
       </c>
       <c r="B95" s="0" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="F95" s="0" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B96" s="0" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="F96" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B97" s="0" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="F97" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B98" s="0" t="s">
-        <v>461</v>
+        <v>487</v>
       </c>
       <c r="F98" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H98" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B99" s="0" t="s">
-        <v>311</v>
-      </c>
-      <c r="C99" s="0" t="s">
-        <v>503</v>
-      </c>
-      <c r="D99" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="F99" s="0" t="s">
         <v>504</v>
       </c>
-      <c r="E99" s="0" t="s">
+      <c r="G99" s="0" t="s">
         <v>505</v>
       </c>
-      <c r="F99" s="0" t="s">
+      <c r="H99" s="0" t="s">
         <v>506</v>
-      </c>
-      <c r="G99" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="H99" s="0" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
+        <v>507</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>508</v>
+      </c>
+      <c r="D100" s="0" t="s">
         <v>509</v>
       </c>
-      <c r="B100" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="C100" s="0" t="s">
+      <c r="E100" s="0" t="s">
         <v>510</v>
       </c>
-      <c r="D100" s="0" t="s">
+      <c r="F100" s="0" t="s">
         <v>511</v>
       </c>
-      <c r="E100" s="0" t="s">
+      <c r="G100" s="0" t="s">
         <v>512</v>
       </c>
-      <c r="F100" s="0" t="s">
-        <v>385</v>
-      </c>
-      <c r="G100" s="0" t="s">
-        <v>386</v>
-      </c>
       <c r="H100" s="0" t="s">
-        <v>387</v>
+        <v>513</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B101" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C101" s="0" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D101" s="0" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="F101" s="0" t="s">
         <v>385</v>
@@ -4997,7 +5003,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B102" s="0" t="s">
         <v>189</v>
@@ -5012,36 +5018,36 @@
         <v>517</v>
       </c>
       <c r="F102" s="0" t="s">
-        <v>518</v>
+        <v>385</v>
+      </c>
+      <c r="G102" s="0" t="s">
+        <v>386</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>519</v>
+        <v>387</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
+        <v>519</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="C103" s="0" t="s">
         <v>520</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="D103" s="0" t="s">
         <v>521</v>
       </c>
-      <c r="C103" s="0" t="s">
+      <c r="E103" s="0" t="s">
         <v>522</v>
       </c>
-      <c r="D103" s="0" t="s">
+      <c r="F103" s="0" t="s">
         <v>523</v>
       </c>
-      <c r="E103" s="0" t="s">
+      <c r="H103" s="0" t="s">
         <v>524</v>
-      </c>
-      <c r="F103" s="0" t="s">
-        <v>385</v>
-      </c>
-      <c r="G103" s="0" t="s">
-        <v>386</v>
-      </c>
-      <c r="H103" s="0" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5061,21 +5067,21 @@
         <v>529</v>
       </c>
       <c r="F104" s="0" t="s">
-        <v>530</v>
+        <v>385</v>
       </c>
       <c r="G104" s="0" t="s">
-        <v>530</v>
+        <v>386</v>
       </c>
       <c r="H104" s="0" t="s">
-        <v>530</v>
+        <v>387</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="B105" s="0" t="s">
         <v>531</v>
-      </c>
-      <c r="B105" s="0" t="s">
-        <v>526</v>
       </c>
       <c r="C105" s="0" t="s">
         <v>532</v>
@@ -5087,305 +5093,314 @@
         <v>534</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="G105" s="0" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H105" s="0" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
+        <v>536</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>531</v>
+      </c>
+      <c r="C106" s="0" t="s">
+        <v>537</v>
+      </c>
+      <c r="D106" s="0" t="s">
+        <v>538</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>539</v>
+      </c>
+      <c r="F106" s="0" t="s">
         <v>535</v>
       </c>
-      <c r="B106" s="0" t="s">
-        <v>526</v>
-      </c>
-      <c r="C106" s="0" t="s">
-        <v>536</v>
-      </c>
-      <c r="D106" s="0" t="s">
-        <v>537</v>
-      </c>
-      <c r="E106" s="0" t="s">
-        <v>538</v>
-      </c>
-      <c r="F106" s="0" t="s">
-        <v>530</v>
-      </c>
       <c r="G106" s="0" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B107" s="0" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C107" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D107" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E107" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="G107" s="0" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H107" s="0" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B108" s="0" t="s">
-        <v>15</v>
+        <v>531</v>
       </c>
       <c r="C108" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E108" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F108" s="0" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="G108" s="0" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="H108" s="0" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B109" s="0" t="s">
         <v>15</v>
       </c>
+      <c r="C109" s="0" t="s">
+        <v>549</v>
+      </c>
+      <c r="D109" s="0" t="s">
+        <v>550</v>
+      </c>
+      <c r="E109" s="0" t="s">
+        <v>551</v>
+      </c>
       <c r="F109" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B110" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="C110" s="0" t="s">
-        <v>555</v>
-      </c>
-      <c r="D110" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="F110" s="0" t="s">
         <v>556</v>
       </c>
-      <c r="E110" s="0" t="s">
+      <c r="G110" s="0" t="s">
         <v>557</v>
       </c>
-      <c r="F110" s="0" t="s">
+      <c r="H110" s="0" t="s">
         <v>558</v>
-      </c>
-      <c r="G110" s="0" t="s">
-        <v>559</v>
-      </c>
-      <c r="H110" s="0" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="C111" s="0" t="s">
+        <v>560</v>
+      </c>
+      <c r="D111" s="0" t="s">
         <v>561</v>
       </c>
-      <c r="B111" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C111" s="0" t="s">
+      <c r="E111" s="0" t="s">
         <v>562</v>
       </c>
-      <c r="D111" s="0" t="s">
+      <c r="F111" s="0" t="s">
         <v>563</v>
       </c>
-      <c r="E111" s="0" t="s">
+      <c r="G111" s="0" t="s">
         <v>564</v>
       </c>
-      <c r="F111" s="0" t="s">
+      <c r="H111" s="0" t="s">
         <v>565</v>
-      </c>
-      <c r="G111" s="0" t="s">
-        <v>566</v>
-      </c>
-      <c r="H111" s="0" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B112" s="0" t="s">
         <v>15</v>
       </c>
+      <c r="C112" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="D112" s="0" t="s">
+        <v>568</v>
+      </c>
+      <c r="E112" s="0" t="s">
+        <v>569</v>
+      </c>
       <c r="F112" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G112" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H112" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B113" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="C113" s="0" t="s">
-        <v>573</v>
-      </c>
-      <c r="D113" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="F113" s="0" t="s">
         <v>574</v>
       </c>
-      <c r="E113" s="0" t="s">
+      <c r="G113" s="0" t="s">
         <v>575</v>
       </c>
-      <c r="F113" s="0" t="s">
+      <c r="H113" s="0" t="s">
         <v>576</v>
-      </c>
-      <c r="G113" s="0" t="s">
-        <v>577</v>
-      </c>
-      <c r="H113" s="0" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
+        <v>577</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="C114" s="0" t="s">
+        <v>578</v>
+      </c>
+      <c r="D114" s="0" t="s">
         <v>579</v>
       </c>
-      <c r="B114" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C114" s="0" t="s">
+      <c r="E114" s="0" t="s">
         <v>580</v>
       </c>
-      <c r="D114" s="0" t="s">
+      <c r="F114" s="0" t="s">
         <v>581</v>
       </c>
-      <c r="E114" s="0" t="s">
+      <c r="G114" s="0" t="s">
         <v>582</v>
       </c>
-      <c r="F114" s="0" t="s">
+      <c r="H114" s="0" t="s">
         <v>583</v>
-      </c>
-      <c r="G114" s="0" t="s">
-        <v>584</v>
-      </c>
-      <c r="H114" s="0" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B115" s="0" t="s">
         <v>15</v>
       </c>
+      <c r="C115" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="D115" s="0" t="s">
+        <v>586</v>
+      </c>
+      <c r="E115" s="0" t="s">
+        <v>587</v>
+      </c>
       <c r="F115" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H115" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B116" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="C116" s="0" t="s">
-        <v>591</v>
-      </c>
-      <c r="D116" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="F116" s="0" t="s">
         <v>592</v>
       </c>
-      <c r="E116" s="0" t="s">
+      <c r="G116" s="0" t="s">
         <v>593</v>
       </c>
-      <c r="F116" s="0" t="s">
+      <c r="H116" s="0" t="s">
         <v>594</v>
-      </c>
-      <c r="G116" s="0" t="s">
-        <v>595</v>
-      </c>
-      <c r="H116" s="0" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
+        <v>595</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="C117" s="0" t="s">
+        <v>596</v>
+      </c>
+      <c r="D117" s="0" t="s">
         <v>597</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="E117" s="0" t="s">
         <v>598</v>
       </c>
-      <c r="C117" s="0" t="s">
+      <c r="F117" s="0" t="s">
         <v>599</v>
       </c>
-      <c r="D117" s="0" t="s">
+      <c r="G117" s="0" t="s">
         <v>600</v>
       </c>
-      <c r="E117" s="0" t="s">
+      <c r="H117" s="0" t="s">
         <v>601</v>
-      </c>
-      <c r="F117" s="0" t="s">
-        <v>602</v>
-      </c>
-      <c r="G117" s="0" t="s">
-        <v>603</v>
-      </c>
-      <c r="H117" s="0" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
+        <v>602</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="C118" s="0" t="s">
+        <v>604</v>
+      </c>
+      <c r="D118" s="0" t="s">
         <v>605</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="E118" s="0" t="s">
         <v>606</v>
       </c>
       <c r="F118" s="0" t="s">
@@ -5403,727 +5418,744 @@
         <v>610</v>
       </c>
       <c r="B119" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="C119" s="0" t="s">
         <v>611</v>
       </c>
-      <c r="D119" s="0" t="s">
+      <c r="F119" s="0" t="s">
         <v>612</v>
       </c>
-      <c r="E119" s="0" t="s">
+      <c r="G119" s="0" t="s">
         <v>613</v>
       </c>
-      <c r="F119" s="0" t="s">
+      <c r="H119" s="0" t="s">
         <v>614</v>
       </c>
-      <c r="G119" s="0" t="s">
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="0" t="s">
         <v>615</v>
-      </c>
-      <c r="H119" s="0" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="125.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="s">
-        <v>617</v>
       </c>
       <c r="B120" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="C120" s="2" t="s">
+      <c r="C120" s="0" t="s">
+        <v>616</v>
+      </c>
+      <c r="D120" s="0" t="s">
+        <v>617</v>
+      </c>
+      <c r="E120" s="0" t="s">
         <v>618</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="F120" s="0" t="s">
         <v>619</v>
       </c>
-      <c r="E120" s="2" t="s">
+      <c r="G120" s="0" t="s">
         <v>620</v>
       </c>
-      <c r="F120" s="2" t="s">
+      <c r="H120" s="0" t="s">
         <v>621</v>
       </c>
-      <c r="G120" s="2" t="s">
+    </row>
+    <row r="121" customFormat="false" ht="125.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="0" t="s">
         <v>622</v>
       </c>
-      <c r="H120" s="2" t="s">
+      <c r="B121" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="C121" s="2" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="121" customFormat="false" ht="112" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="s">
+      <c r="D121" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="E121" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="112" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="0" t="s">
+        <v>629</v>
+      </c>
+      <c r="B122" s="0" t="s">
         <v>341</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="H121" s="2" t="s">
+      <c r="C122" s="2" t="s">
         <v>630</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="s">
+      <c r="D122" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B122" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="C122" s="2" t="s">
+      <c r="E122" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="F122" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="E122" s="2" t="s">
+      <c r="G122" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="F122" s="2" t="s">
+      <c r="H122" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="G122" s="2" t="s">
+    </row>
+    <row r="123" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="0" t="s">
         <v>636</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="s">
-        <v>638</v>
       </c>
       <c r="B123" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C123" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="F123" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E123" s="2" t="s">
+      <c r="G123" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="F123" s="2" t="s">
+      <c r="H123" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
+        <v>643</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="D124" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="E124" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="C124" s="2" t="s">
+      <c r="F124" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="D124" s="2" t="s">
+      <c r="G124" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="E124" s="2" t="s">
+      <c r="H124" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="F124" s="2" t="s">
+    </row>
+    <row r="125" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="0" t="s">
         <v>650</v>
       </c>
-      <c r="G124" s="2" t="s">
+      <c r="B125" s="0" t="s">
         <v>651</v>
       </c>
-      <c r="H124" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="s">
+      <c r="D125" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="E125" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="C125" s="0" t="s">
+      <c r="F125" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="D125" s="0" t="s">
+      <c r="G125" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="E125" s="0" t="s">
+      <c r="H125" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="F125" s="0" t="s">
-        <v>658</v>
-      </c>
-      <c r="G125" s="0" t="s">
-        <v>659</v>
-      </c>
-      <c r="H125" s="0" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
+        <v>658</v>
+      </c>
+      <c r="B126" s="0" t="s">
+        <v>659</v>
+      </c>
+      <c r="C126" s="0" t="s">
+        <v>660</v>
+      </c>
+      <c r="D126" s="0" t="s">
         <v>661</v>
       </c>
-      <c r="B126" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="C126" s="0" t="s">
+      <c r="E126" s="0" t="s">
         <v>662</v>
       </c>
-      <c r="D126" s="0" t="s">
+      <c r="F126" s="0" t="s">
         <v>663</v>
       </c>
-      <c r="E126" s="0" t="s">
+      <c r="G126" s="0" t="s">
         <v>664</v>
       </c>
-      <c r="F126" s="0" t="s">
+      <c r="H126" s="0" t="s">
         <v>665</v>
-      </c>
-      <c r="G126" s="0" t="s">
-        <v>666</v>
-      </c>
-      <c r="H126" s="0" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B127" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C127" s="0" t="s">
+        <v>667</v>
+      </c>
+      <c r="D127" s="0" t="s">
+        <v>668</v>
+      </c>
+      <c r="E127" s="0" t="s">
         <v>669</v>
       </c>
-      <c r="D127" s="0" t="s">
+      <c r="F127" s="0" t="s">
         <v>670</v>
       </c>
-      <c r="E127" s="0" t="s">
+      <c r="G127" s="0" t="s">
         <v>671</v>
       </c>
-      <c r="F127" s="0" t="s">
+      <c r="H127" s="0" t="s">
         <v>672</v>
       </c>
-      <c r="G127" s="0" t="s">
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="0" t="s">
         <v>673</v>
-      </c>
-      <c r="H127" s="0" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="s">
-        <v>675</v>
       </c>
       <c r="B128" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C128" s="0" t="s">
+        <v>674</v>
+      </c>
+      <c r="D128" s="0" t="s">
+        <v>675</v>
+      </c>
+      <c r="E128" s="0" t="s">
         <v>676</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="F128" s="0" t="s">
         <v>677</v>
       </c>
-      <c r="E128" s="2" t="s">
+      <c r="G128" s="0" t="s">
         <v>678</v>
       </c>
-      <c r="F128" s="2" t="s">
+      <c r="H128" s="0" t="s">
         <v>679</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B129" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C129" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="E129" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="D129" s="2" t="s">
+      <c r="F129" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="E129" s="2" t="s">
+      <c r="G129" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="F129" s="2" t="s">
+      <c r="H129" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
+        <v>687</v>
+      </c>
+      <c r="B130" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="D130" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="E130" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="0" t="s">
+        <v>694</v>
+      </c>
+      <c r="B131" s="0" t="s">
         <v>311</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="G130" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="H130" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="131" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="s">
+      <c r="D131" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="B131" s="0" t="s">
-        <v>189</v>
-      </c>
-      <c r="C131" s="2" t="s">
+      <c r="E131" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="F131" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="E131" s="2" t="s">
+      <c r="G131" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="F131" s="2" t="s">
+      <c r="H131" s="2" t="s">
         <v>700</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B132" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C132" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="F132" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="E132" s="2" t="s">
+      <c r="G132" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="F132" s="2" t="s">
+      <c r="H132" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B133" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C133" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="E133" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="F133" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="E133" s="2" t="s">
+      <c r="G133" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="F133" s="2" t="s">
+      <c r="H133" s="2" t="s">
         <v>714</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B134" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C134" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="E134" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="F134" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="E134" s="2" t="s">
+      <c r="G134" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="F134" s="2" t="s">
+      <c r="H134" s="2" t="s">
         <v>721</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B135" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C135" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="F135" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="E135" s="2" t="s">
+      <c r="G135" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="F135" s="2" t="s">
+      <c r="H135" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B136" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C136" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="D136" s="2" t="s">
+      <c r="F136" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="E136" s="2" t="s">
+      <c r="G136" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="F136" s="2" t="s">
+      <c r="H136" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="G136" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="H136" s="2" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B137" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C137" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="E137" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="F137" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="E137" s="2" t="s">
+      <c r="G137" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="F137" s="2" t="s">
+      <c r="H137" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B138" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B139" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C139" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="G139" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="D139" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="F139" s="2" t="s">
+      <c r="H139" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="H139" s="2" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B140" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C140" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="E140" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="D140" s="2" t="s">
+      <c r="F140" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="E140" s="2" t="s">
+      <c r="G140" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="F140" s="2" t="s">
+      <c r="H140" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>759</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B141" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C141" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="E141" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="D141" s="2" t="s">
+      <c r="F141" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="E141" s="2" t="s">
+      <c r="G141" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="F141" s="2" t="s">
+      <c r="H141" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="H141" s="2" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B142" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C142" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="E142" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="D142" s="2" t="s">
+      <c r="F142" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="E142" s="2" t="s">
+      <c r="G142" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="F142" s="2" t="s">
+      <c r="H142" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="G142" s="2" t="s">
+    </row>
+    <row r="143" customFormat="false" ht="28.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="0" t="s">
         <v>773</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="0" t="s">
-        <v>775</v>
       </c>
       <c r="B143" s="0" t="s">
         <v>189</v>
       </c>
       <c r="C143" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="E143" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="D143" s="2" t="s">
+      <c r="F143" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="E143" s="2" t="s">
+      <c r="G143" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="F143" s="2" t="s">
+      <c r="H143" s="2" t="s">
         <v>779</v>
-      </c>
-      <c r="G143" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
+        <v>780</v>
+      </c>
+      <c r="B144" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="D144" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="B144" s="0" t="s">
+      <c r="E144" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="C144" s="2" t="s">
+      <c r="F144" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="D144" s="2" t="s">
+      <c r="G144" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="E144" s="2" t="s">
+      <c r="H144" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
+        <v>787</v>
+      </c>
+      <c r="B145" s="0" t="s">
+        <v>788</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="D145" s="2" t="s">
         <v>790</v>
       </c>
-      <c r="B145" s="0" t="s">
-        <v>341</v>
-      </c>
-      <c r="C145" s="2" t="s">
+      <c r="E145" s="2" t="s">
         <v>791</v>
       </c>
-      <c r="D145" s="2" t="s">
+      <c r="F145" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="E145" s="2" t="s">
+      <c r="G145" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="F145" s="2" t="s">
+      <c r="H145" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="G145" s="2" t="s">
+    </row>
+    <row r="146" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="0" t="s">
         <v>795</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="0" t="s">
-        <v>797</v>
       </c>
       <c r="B146" s="0" t="s">
         <v>341</v>
       </c>
-      <c r="C146" s="0" t="s">
+      <c r="C146" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="E146" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="D146" s="0" t="s">
+      <c r="F146" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="E146" s="0" t="s">
+      <c r="G146" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="F146" s="0" t="s">
+      <c r="H146" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="G146" s="0" t="s">
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="0" t="s">
         <v>802</v>
       </c>
-      <c r="H146" s="0" t="s">
+      <c r="B147" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="C147" s="0" t="s">
         <v>803</v>
+      </c>
+      <c r="D147" s="0" t="s">
+        <v>804</v>
+      </c>
+      <c r="E147" s="0" t="s">
+        <v>805</v>
+      </c>
+      <c r="F147" s="0" t="s">
+        <v>806</v>
+      </c>
+      <c r="G147" s="0" t="s">
+        <v>807</v>
+      </c>
+      <c r="H147" s="0" t="s">
+        <v>808</v>
       </c>
     </row>
   </sheetData>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Quest.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Quest.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Quest.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Quest.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.307</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Quest.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Quest.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.307</t>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">Main Quest</t>
